--- a/数据表/Datas/BattleActionConfig_战斗行动配置.xlsx
+++ b/数据表/Datas/BattleActionConfig_战斗行动配置.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\Seek-Battle-Evacuate\数据表\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -99,7 +104,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>行动</t>
@@ -108,7 +113,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>ID</t>
@@ -119,7 +124,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>显示名</t>
@@ -130,7 +135,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>行动类型</t>
@@ -141,7 +146,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>目标选择方式</t>
@@ -155,7 +160,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>消耗</t>
@@ -166,7 +171,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>目标属性</t>
@@ -177,7 +182,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>目标值</t>
@@ -188,7 +193,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>用于缩放的来源属性</t>
@@ -199,7 +204,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>来源属性千分比，负数表示减少目标值</t>
@@ -210,7 +215,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>附加状态</t>
@@ -221,7 +226,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>状态持续轮数</t>
@@ -232,7 +237,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>普通攻击</t>
@@ -243,7 +248,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>攻击</t>
@@ -254,7 +259,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>单个敌方</t>
@@ -265,7 +270,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>当前生命</t>
@@ -275,7 +280,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>攻击力</t>
@@ -285,7 +290,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>无</t>
@@ -296,7 +301,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>技能</t>
@@ -305,7 +310,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -316,7 +321,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>技能</t>
@@ -327,7 +332,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>速度</t>
@@ -338,7 +343,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>技能</t>
@@ -347,7 +352,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>2</t>
@@ -358,7 +363,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>单个友方</t>
@@ -369,7 +374,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>魔力</t>
@@ -380,7 +385,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>技能</t>
@@ -389,7 +394,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>3</t>
@@ -400,7 +405,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>全体敌方</t>
@@ -411,7 +416,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>技能</t>
@@ -420,7 +425,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>4</t>
@@ -431,7 +436,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>无</t>
@@ -441,7 +446,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>眩晕</t>
@@ -452,7 +457,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人攻击</t>
@@ -463,7 +468,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人魔法</t>
@@ -488,37 +493,37 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF006100"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F4E78"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF595959"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF202020"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
@@ -675,18 +680,18 @@
     <font>
       <sz val="12"/>
       <color rgb="FF202020"/>
-      <name val="PingFang SC Regular"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="PingFang SC Regular"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1832,15 +1837,15 @@
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
     <col min="2" max="2" width="10" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.9852941176471" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.9833333333333" style="2" customWidth="1"/>
     <col min="4" max="5" width="19" style="2" customWidth="1"/>
     <col min="6" max="6" width="10" style="2" customWidth="1"/>
-    <col min="7" max="7" width="13.2279411764706" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.1102941176471" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.0735294117647" style="2" customWidth="1"/>
-    <col min="10" max="10" width="33.5735294117647" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.6617647058824" style="2" customWidth="1"/>
-    <col min="12" max="12" width="20.5808823529412" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.225" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.1083333333333" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.075" style="2" customWidth="1"/>
+    <col min="10" max="10" width="33.575" style="2" customWidth="1"/>
+    <col min="11" max="11" width="10.6583333333333" style="2" customWidth="1"/>
+    <col min="12" max="12" width="20.5833333333333" style="2" customWidth="1"/>
     <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -2109,7 +2114,7 @@
         <v>43</v>
       </c>
       <c r="F10" s="18">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G10" s="18" t="s">
         <v>36</v>
